--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_40.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2387262.717401931</v>
+        <v>2380353.246291292</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9774782.687313251</v>
+        <v>9774782.687313253</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9774782.687313251</v>
+        <v>9774782.687313253</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138604.377786998</v>
+        <v>138604.3777869989</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138604.377786998</v>
+        <v>138604.3777869989</v>
       </c>
     </row>
     <row r="11">
@@ -702,13 +702,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>215.3817731139785</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -793,16 +793,16 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>385</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>378.7695628633035</v>
       </c>
       <c r="Y3" t="n">
-        <v>97.030640593115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -857,10 +857,10 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>325.839266425598</v>
+        <v>324.2480957795422</v>
       </c>
       <c r="R4" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>277.9274879340253</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
-        <v>229.8510241668239</v>
+        <v>258.5572155522385</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
@@ -979,16 +979,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>332.0195022027719</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>185.9212948591249</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1033,7 +1033,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>385</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1094,10 +1094,10 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q7" t="n">
-        <v>324.2480957795422</v>
+        <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1219,13 +1219,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>170.8861760628762</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>145.9153024145155</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>385</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172882</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1368,13 +1368,13 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D11" t="n">
         <v>60.33915573984979</v>
       </c>
       <c r="E11" t="n">
-        <v>54.36328960686865</v>
+        <v>58.32868099228319</v>
       </c>
       <c r="F11" t="n">
         <v>54.88962870801186</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>11.09991244551929</v>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U12" t="n">
         <v>50.21035976018675</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>405.3577652175138</v>
+        <v>118.0355277429563</v>
       </c>
       <c r="U15" t="n">
         <v>50.21035976018675</v>
@@ -1750,7 +1750,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1842,7 +1842,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>99.47457824299391</v>
+        <v>103.4399696284084</v>
       </c>
       <c r="D17" t="n">
         <v>60.33915573984979</v>
@@ -1857,7 +1857,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>206.6512890796133</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2085,13 +2085,13 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E20" t="n">
-        <v>54.36328960686865</v>
+        <v>58.32868099228319</v>
       </c>
       <c r="F20" t="n">
         <v>54.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
         <v>58.00965870352741</v>
@@ -2161,22 +2161,22 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2398,10 +2398,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>64.74007562773993</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>312.1153765987053</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
         <v>55.35776521751382</v>
@@ -2738,25 +2738,25 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>105.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>75.08705884799663</v>
       </c>
       <c r="O28" t="n">
         <v>322.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>369.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>407.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>17.15730625609968</v>
+        <v>408.6021279811511</v>
       </c>
       <c r="S28" t="n">
         <v>44.37347970285543</v>
@@ -2847,7 +2847,7 @@
         <v>331.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>311.8510241668239</v>
+        <v>306.3468155522964</v>
       </c>
       <c r="W29" t="n">
         <v>320.3734759809475</v>
@@ -2856,7 +2856,7 @@
         <v>274.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>187.8132240682209</v>
+        <v>193.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2875,7 +2875,7 @@
         <v>29.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>24.67209722191262</v>
+        <v>24.67209722187968</v>
       </c>
       <c r="F30" t="n">
         <v>21.63624233787687</v>
@@ -2975,28 +2975,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>105.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>253.1850752716849</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>369.4478973282775</v>
+        <v>188.7210273581823</v>
       </c>
       <c r="Q31" t="n">
         <v>407.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>339.6028703351146</v>
+        <v>408.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>44.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3036,7 +3036,7 @@
         <v>86.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>86.88962870801186</v>
+        <v>81.38542009342628</v>
       </c>
       <c r="G32" t="n">
         <v>85.75737228701621</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>171.343959187798</v>
+        <v>176.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>268.6755817285639</v>
@@ -3163,13 +3163,13 @@
         <v>82.21035976018675</v>
       </c>
       <c r="V33" t="n">
-        <v>96.51066719152016</v>
+        <v>96.51066719148727</v>
       </c>
       <c r="W33" t="n">
         <v>114.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>101.8627394453583</v>
+        <v>101.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>81.39139276613435</v>
@@ -3215,25 +3215,25 @@
         <v>105.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>253.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>322.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>350.318064233928</v>
+        <v>369.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>407.839266425598</v>
+        <v>313.268960357639</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>44.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3397,7 +3397,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>130.7200350992081</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
         <v>64.51066719152016</v>
@@ -3409,7 +3409,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3513,7 +3513,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
         <v>58.00965870352741</v>
@@ -3558,7 +3558,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V38" t="n">
-        <v>279.8510241668239</v>
+        <v>283.8164155522384</v>
       </c>
       <c r="W38" t="n">
         <v>288.3734759809475</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
-        <v>197.0736753036327</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T39" t="n">
         <v>55.35776521751382</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="40">
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>49.39139276613435</v>
+        <v>119.3970580696643</v>
       </c>
     </row>
     <row r="43">
@@ -3990,7 +3990,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4063,13 +4063,13 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>55.35776521751382</v>
+        <v>128.3992854050794</v>
       </c>
       <c r="U45" t="n">
         <v>50.21035976018675</v>
@@ -4120,7 +4120,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4321,22 +4321,22 @@
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K2" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="L2" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="M2" t="n">
         <v>411.95</v>
       </c>
       <c r="N2" t="n">
-        <v>793.0999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1158.85</v>
+        <v>793.1</v>
       </c>
       <c r="P2" t="n">
         <v>1158.85</v>
@@ -4345,10 +4345,10 @@
         <v>1540</v>
       </c>
       <c r="R2" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T2" t="n">
         <v>1226.636423316867</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.1195817084329</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="C3" t="n">
-        <v>250.1195817084329</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="D3" t="n">
-        <v>250.1195817084329</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="E3" t="n">
-        <v>250.1195817084329</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="F3" t="n">
-        <v>250.1195817084329</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="G3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4436,16 +4436,16 @@
         <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>400.8938473128077</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W3" t="n">
-        <v>368.1937029594455</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X3" t="n">
-        <v>348.1303297822864</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="Y3" t="n">
-        <v>250.1195817084329</v>
+        <v>359.8298342171994</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>836.3445499022765</v>
+        <v>690.4569442158812</v>
       </c>
       <c r="C4" t="n">
-        <v>836.3445499022765</v>
+        <v>816.458950034317</v>
       </c>
       <c r="D4" t="n">
-        <v>949.6636940272766</v>
+        <v>929.7780941593171</v>
       </c>
       <c r="E4" t="n">
-        <v>1067.49259823869</v>
+        <v>1025.509693460663</v>
       </c>
       <c r="F4" t="n">
-        <v>1067.49259823869</v>
+        <v>1025.509693460663</v>
       </c>
       <c r="G4" t="n">
-        <v>1067.49259823869</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="H4" t="n">
-        <v>1067.49259823869</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J4" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
@@ -4500,7 +4500,7 @@
         <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4509,22 +4509,22 @@
         <v>68.05025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>68.05025509417312</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>314.6014477324597</v>
+        <v>256.125934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>513.4228406184056</v>
+        <v>256.125934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>685.313758878083</v>
+        <v>428.0168525126554</v>
       </c>
       <c r="X4" t="n">
-        <v>836.3445499022765</v>
+        <v>579.0476435368489</v>
       </c>
       <c r="Y4" t="n">
-        <v>836.3445499022765</v>
+        <v>690.4569442158812</v>
       </c>
     </row>
     <row r="5">
@@ -4558,7 +4558,7 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="K5" t="n">
         <v>396.55</v>
@@ -4591,7 +4591,7 @@
         <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
         <v>742.7249882507717</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>366.1732345482545</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>366.1732345482545</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>366.1732345482545</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>554.1226081268142</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T6" t="n">
-        <v>789.9952208079459</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>789.7827362016966</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>775.1254966143025</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>386.2366077254136</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X6" t="n">
-        <v>366.1732345482545</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>366.1732345482545</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,22 +4692,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>678.3748087061448</v>
+        <v>279.3512084368344</v>
       </c>
       <c r="C7" t="n">
-        <v>804.3768145245806</v>
+        <v>279.3512084368344</v>
       </c>
       <c r="D7" t="n">
-        <v>804.3768145245806</v>
+        <v>392.6703525618345</v>
       </c>
       <c r="E7" t="n">
-        <v>804.3768145245806</v>
+        <v>510.4992567732476</v>
       </c>
       <c r="F7" t="n">
-        <v>804.3768145245806</v>
+        <v>634.860229365183</v>
       </c>
       <c r="G7" t="n">
-        <v>957.7833804114658</v>
+        <v>788.2667952520683</v>
       </c>
       <c r="H7" t="n">
         <v>957.7833804114658</v>
@@ -4737,31 +4737,31 @@
         <v>688.2244684451448</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>148.1753601418887</v>
+        <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>394.7265527801753</v>
+        <v>30.8</v>
       </c>
       <c r="V7" t="n">
-        <v>394.7265527801753</v>
+        <v>30.8</v>
       </c>
       <c r="W7" t="n">
-        <v>566.6174710398527</v>
+        <v>30.8</v>
       </c>
       <c r="X7" t="n">
-        <v>566.6174710398527</v>
+        <v>181.8307910241935</v>
       </c>
       <c r="Y7" t="n">
-        <v>566.6174710398527</v>
+        <v>181.8307910241935</v>
       </c>
     </row>
     <row r="8">
@@ -4795,16 +4795,16 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="L8" t="n">
-        <v>411.95</v>
+        <v>411.9499999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>793.1</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>1174.25</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>897.189519579215</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="C9" t="n">
-        <v>532.4421332706097</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="D9" t="n">
-        <v>532.4421332706097</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="E9" t="n">
-        <v>532.4421332706097</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="F9" t="n">
-        <v>359.8298342171994</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4904,22 +4904,22 @@
         <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>964.8227613033797</v>
+        <v>581.3457564725855</v>
       </c>
       <c r="U9" t="n">
-        <v>964.6102766971304</v>
+        <v>581.1332718663363</v>
       </c>
       <c r="V9" t="n">
-        <v>949.9530371097363</v>
+        <v>566.4760322789422</v>
       </c>
       <c r="W9" t="n">
-        <v>917.2528927563742</v>
+        <v>533.77588792558</v>
       </c>
       <c r="X9" t="n">
-        <v>897.189519579215</v>
+        <v>513.7125147484209</v>
       </c>
       <c r="Y9" t="n">
-        <v>897.189519579215</v>
+        <v>513.7125147484209</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>902.9689267488908</v>
+        <v>781.158653282735</v>
       </c>
       <c r="C10" t="n">
-        <v>1028.970932567327</v>
+        <v>907.1606591011708</v>
       </c>
       <c r="D10" t="n">
-        <v>1142.290076692327</v>
+        <v>907.1606591011708</v>
       </c>
       <c r="E10" t="n">
-        <v>1260.11898090374</v>
+        <v>1024.989563312584</v>
       </c>
       <c r="F10" t="n">
-        <v>1260.11898090374</v>
+        <v>1149.350535904519</v>
       </c>
       <c r="G10" t="n">
-        <v>1260.11898090374</v>
+        <v>1149.350535904519</v>
       </c>
       <c r="H10" t="n">
-        <v>1429.635566063137</v>
+        <v>1318.867121063917</v>
       </c>
       <c r="I10" t="n">
-        <v>1429.635566063137</v>
+        <v>1540</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063137</v>
+        <v>1540</v>
       </c>
       <c r="K10" t="n">
-        <v>1540.000000000006</v>
+        <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P10" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>218.8756791588049</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>465.4268717970915</v>
+        <v>314.6014477324597</v>
       </c>
       <c r="V10" t="n">
-        <v>465.4268717970915</v>
+        <v>513.4228406184056</v>
       </c>
       <c r="W10" t="n">
-        <v>637.3177900567689</v>
+        <v>518.3705245922494</v>
       </c>
       <c r="X10" t="n">
-        <v>788.3485810809624</v>
+        <v>669.4013156164428</v>
       </c>
       <c r="Y10" t="n">
-        <v>791.2115890825987</v>
+        <v>669.4013156164428</v>
       </c>
     </row>
     <row r="11">
@@ -5011,10 +5011,10 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E11" t="n">
         <v>213.0600603015712</v>
@@ -5038,19 +5038,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>618.3311712710653</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M11" t="n">
-        <v>1129.18</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N11" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O11" t="n">
-        <v>2236</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P11" t="n">
-        <v>2236</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5090,16 +5090,16 @@
         <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
-        <v>108.0308712378206</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D12" t="n">
-        <v>108.0308712378206</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E12" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="F12" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="G12" t="n">
         <v>44.72</v>
@@ -5141,22 +5141,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>154.1485167851397</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5284,7 +5284,7 @@
         <v>1704.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2236</v>
+        <v>1704.95</v>
       </c>
       <c r="P14" t="n">
         <v>2236</v>
@@ -5293,7 +5293,7 @@
         <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S14" t="n">
         <v>2085.68327354774</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="G15" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="H15" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="I15" t="n">
         <v>44.72</v>
@@ -5378,22 +5378,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U15" t="n">
-        <v>422.9747211415747</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V15" t="n">
-        <v>357.8124310491301</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W15" t="n">
-        <v>274.6072361907174</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X15" t="n">
-        <v>204.0388125085078</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y15" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5485,19 +5485,19 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F17" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G17" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H17" t="n">
         <v>44.72</v>
@@ -5506,25 +5506,25 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L17" t="n">
-        <v>44.72</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M17" t="n">
-        <v>555.568828728935</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N17" t="n">
-        <v>1108.978828728935</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O17" t="n">
-        <v>1662.388828728935</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="P17" t="n">
-        <v>2215.798828728935</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C18" t="n">
-        <v>264.0395817084329</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D18" t="n">
-        <v>264.0395817084329</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5728,10 +5728,10 @@
         <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G20" t="n">
         <v>103.3156148520479</v>
@@ -5746,22 +5746,22 @@
         <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>598.13</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="L20" t="n">
-        <v>1151.54</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="M20" t="n">
-        <v>1662.388828728935</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N20" t="n">
-        <v>2215.79882872894</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5804,19 +5804,19 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D21" t="n">
-        <v>461.5662247731743</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E21" t="n">
-        <v>461.5662247731743</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F21" t="n">
-        <v>264.0395817084329</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G21" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H21" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I21" t="n">
         <v>44.72</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F23" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5980,22 +5980,22 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L23" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M23" t="n">
-        <v>137.1709049473099</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N23" t="n">
-        <v>690.5809049473183</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O23" t="n">
-        <v>1243.990904947326</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>275.2516144816847</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C24" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D24" t="n">
-        <v>264.0395817084329</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="E24" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G24" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H24" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I24" t="n">
         <v>44.72</v>
@@ -6086,25 +6086,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>685.6179012866319</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>629.7009667234867</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U24" t="n">
-        <v>578.9834316121869</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V24" t="n">
-        <v>513.8211415197422</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W24" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>360.0475229791199</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y24" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="25">
@@ -6220,22 +6220,22 @@
         <v>445.0691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>1110.349113037656</v>
+        <v>445.0691130376557</v>
       </c>
       <c r="L26" t="n">
         <v>1110.349113037656</v>
       </c>
       <c r="M26" t="n">
-        <v>1621.197941766591</v>
+        <v>1110.349113037656</v>
       </c>
       <c r="N26" t="n">
-        <v>1621.197941766591</v>
+        <v>1110.349113037656</v>
       </c>
       <c r="O26" t="n">
-        <v>2249.400904947332</v>
+        <v>1775.629113037664</v>
       </c>
       <c r="P26" t="n">
-        <v>2249.400904947332</v>
+        <v>2440.909113037674</v>
       </c>
       <c r="Q26" t="n">
         <v>2688</v>
@@ -6293,10 +6293,10 @@
         <v>53.76</v>
       </c>
       <c r="I27" t="n">
-        <v>53.76</v>
+        <v>59.29119898333113</v>
       </c>
       <c r="J27" t="n">
-        <v>177.7165201752989</v>
+        <v>183.2477191586301</v>
       </c>
       <c r="K27" t="n">
         <v>372.4405352530135</v>
@@ -6381,22 +6381,22 @@
         <v>1431.431843630702</v>
       </c>
       <c r="L28" t="n">
-        <v>1431.431843630702</v>
+        <v>1324.818077814764</v>
       </c>
       <c r="M28" t="n">
-        <v>1226.753448274591</v>
+        <v>1324.818077814764</v>
       </c>
       <c r="N28" t="n">
-        <v>1226.753448274591</v>
+        <v>1248.972563826889</v>
       </c>
       <c r="O28" t="n">
-        <v>901.0508582957884</v>
+        <v>923.2699738480854</v>
       </c>
       <c r="P28" t="n">
-        <v>527.8711640248011</v>
+        <v>923.2699738480854</v>
       </c>
       <c r="Q28" t="n">
-        <v>115.9123090494496</v>
+        <v>511.3111188727339</v>
       </c>
       <c r="R28" t="n">
         <v>98.58169666955095</v>
@@ -6454,22 +6454,22 @@
         <v>53.76</v>
       </c>
       <c r="J29" t="n">
-        <v>445.0691130376557</v>
+        <v>53.76</v>
       </c>
       <c r="K29" t="n">
-        <v>1110.349113037656</v>
+        <v>719.0399999999998</v>
       </c>
       <c r="L29" t="n">
-        <v>1775.629113037656</v>
+        <v>1384.32</v>
       </c>
       <c r="M29" t="n">
-        <v>1775.629113037656</v>
+        <v>1895.168828728935</v>
       </c>
       <c r="N29" t="n">
-        <v>2022.719999999999</v>
+        <v>2022.719999999998</v>
       </c>
       <c r="O29" t="n">
-        <v>2688</v>
+        <v>2022.719999999998</v>
       </c>
       <c r="P29" t="n">
         <v>2688</v>
@@ -6478,25 +6478,25 @@
         <v>2688</v>
       </c>
       <c r="R29" t="n">
-        <v>2688</v>
+        <v>2688.000000000059</v>
       </c>
       <c r="S29" t="n">
-        <v>2509.365487068361</v>
+        <v>2509.365487068419</v>
       </c>
       <c r="T29" t="n">
-        <v>2237.976010574862</v>
+        <v>2237.976010574921</v>
       </c>
       <c r="U29" t="n">
-        <v>1903.409044364144</v>
+        <v>1903.409044364203</v>
       </c>
       <c r="V29" t="n">
-        <v>1588.408009852201</v>
+        <v>1593.9678165336</v>
       </c>
       <c r="W29" t="n">
-        <v>1264.798438154274</v>
+        <v>1270.358244835673</v>
       </c>
       <c r="X29" t="n">
-        <v>987.7460811232962</v>
+        <v>993.3058878046958</v>
       </c>
       <c r="Y29" t="n">
         <v>798.035753781659</v>
@@ -6509,13 +6509,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>196.4403656206666</v>
+        <v>196.4403656206333</v>
       </c>
       <c r="C30" t="n">
-        <v>152.9051005241824</v>
+        <v>152.9051005241491</v>
       </c>
       <c r="D30" t="n">
-        <v>122.6650127487252</v>
+        <v>122.6650127486919</v>
       </c>
       <c r="E30" t="n">
         <v>97.74370242356093</v>
@@ -6554,31 +6554,31 @@
         <v>1209.192420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351834</v>
       </c>
       <c r="R30" t="n">
-        <v>983.1339251171403</v>
+        <v>983.133925117107</v>
       </c>
       <c r="S30" t="n">
-        <v>833.0692786882399</v>
+        <v>833.0692786882066</v>
       </c>
       <c r="T30" t="n">
-        <v>744.8291118018624</v>
+        <v>744.8291118018291</v>
       </c>
       <c r="U30" t="n">
-        <v>661.7883443673303</v>
+        <v>661.788344367297</v>
       </c>
       <c r="V30" t="n">
-        <v>564.3028219516534</v>
+        <v>564.3028219516201</v>
       </c>
       <c r="W30" t="n">
-        <v>448.7743947700085</v>
+        <v>448.7743947699752</v>
       </c>
       <c r="X30" t="n">
-        <v>345.8827387645665</v>
+        <v>345.8827387645332</v>
       </c>
       <c r="Y30" t="n">
-        <v>263.6692107179662</v>
+        <v>263.6692107179329</v>
       </c>
     </row>
     <row r="31">
@@ -6618,25 +6618,25 @@
         <v>1431.431843630702</v>
       </c>
       <c r="L31" t="n">
-        <v>1431.431843630702</v>
+        <v>1324.818077814764</v>
       </c>
       <c r="M31" t="n">
-        <v>1226.753448274591</v>
+        <v>1324.818077814764</v>
       </c>
       <c r="N31" t="n">
-        <v>1226.753448274591</v>
+        <v>1069.075577540335</v>
       </c>
       <c r="O31" t="n">
-        <v>1226.753448274591</v>
+        <v>1069.075577540335</v>
       </c>
       <c r="P31" t="n">
-        <v>853.5737540036041</v>
+        <v>878.4482771785345</v>
       </c>
       <c r="Q31" t="n">
-        <v>441.6148990282526</v>
+        <v>466.4894222031829</v>
       </c>
       <c r="R31" t="n">
-        <v>98.58169666955095</v>
+        <v>53.76</v>
       </c>
       <c r="S31" t="n">
         <v>53.76</v>
@@ -6667,16 +6667,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>632.3798821093615</v>
+        <v>626.8200754279619</v>
       </c>
       <c r="C32" t="n">
-        <v>499.577277823509</v>
+        <v>494.0174711421095</v>
       </c>
       <c r="D32" t="n">
-        <v>406.3054033388123</v>
+        <v>400.7455966574127</v>
       </c>
       <c r="E32" t="n">
-        <v>319.0697572712681</v>
+        <v>313.5099505898686</v>
       </c>
       <c r="F32" t="n">
         <v>231.3024555460037</v>
@@ -6691,22 +6691,22 @@
         <v>53.76</v>
       </c>
       <c r="J32" t="n">
-        <v>445.0691130376557</v>
+        <v>53.76</v>
       </c>
       <c r="K32" t="n">
-        <v>1110.349113037656</v>
+        <v>53.76</v>
       </c>
       <c r="L32" t="n">
-        <v>1110.349113037656</v>
+        <v>53.76</v>
       </c>
       <c r="M32" t="n">
-        <v>1584.120904947331</v>
+        <v>564.608828728935</v>
       </c>
       <c r="N32" t="n">
-        <v>1584.120904947331</v>
+        <v>918.840904947328</v>
       </c>
       <c r="O32" t="n">
-        <v>2249.400904947332</v>
+        <v>1584.12090494733</v>
       </c>
       <c r="P32" t="n">
         <v>2249.400904947332</v>
@@ -6715,28 +6715,28 @@
         <v>2688</v>
       </c>
       <c r="R32" t="n">
-        <v>2688.000000000061</v>
+        <v>2688</v>
       </c>
       <c r="S32" t="n">
-        <v>2514.92529374976</v>
+        <v>2509.365487068361</v>
       </c>
       <c r="T32" t="n">
-        <v>2243.535817256261</v>
+        <v>2237.976010574862</v>
       </c>
       <c r="U32" t="n">
-        <v>1908.968851045543</v>
+        <v>1903.409044364144</v>
       </c>
       <c r="V32" t="n">
-        <v>1593.9678165336</v>
+        <v>1588.408009852201</v>
       </c>
       <c r="W32" t="n">
-        <v>1270.358244835673</v>
+        <v>1264.798438154274</v>
       </c>
       <c r="X32" t="n">
-        <v>993.3058878046958</v>
+        <v>987.7460811232962</v>
       </c>
       <c r="Y32" t="n">
-        <v>798.035753781659</v>
+        <v>792.4759471002594</v>
       </c>
     </row>
     <row r="33">
@@ -6767,49 +6767,49 @@
         <v>53.76</v>
       </c>
       <c r="I33" t="n">
-        <v>59.29119898330157</v>
+        <v>59.29119898329793</v>
       </c>
       <c r="J33" t="n">
-        <v>183.2477191586005</v>
+        <v>183.2477191585969</v>
       </c>
       <c r="K33" t="n">
-        <v>372.4405352529839</v>
+        <v>372.4405352529803</v>
       </c>
       <c r="L33" t="n">
-        <v>643.790996848184</v>
+        <v>643.7909968481804</v>
       </c>
       <c r="M33" t="n">
-        <v>729.8715385910433</v>
+        <v>729.8715385910397</v>
       </c>
       <c r="N33" t="n">
-        <v>863.1518231986116</v>
+        <v>863.151823198608</v>
       </c>
       <c r="O33" t="n">
-        <v>1102.194274882331</v>
+        <v>1102.194274882327</v>
       </c>
       <c r="P33" t="n">
-        <v>1214.723619351837</v>
+        <v>1214.723619351834</v>
       </c>
       <c r="Q33" t="n">
-        <v>1214.723619351837</v>
+        <v>1214.723619351834</v>
       </c>
       <c r="R33" t="n">
-        <v>983.1339251171107</v>
+        <v>983.1339251171071</v>
       </c>
       <c r="S33" t="n">
-        <v>833.0692786882104</v>
+        <v>833.0692786882067</v>
       </c>
       <c r="T33" t="n">
-        <v>744.8291118018328</v>
+        <v>744.8291118018292</v>
       </c>
       <c r="U33" t="n">
-        <v>661.7883443673007</v>
+        <v>661.7883443672971</v>
       </c>
       <c r="V33" t="n">
-        <v>564.3028219516239</v>
+        <v>564.3028219516534</v>
       </c>
       <c r="W33" t="n">
-        <v>448.7743947699789</v>
+        <v>448.7743947700085</v>
       </c>
       <c r="X33" t="n">
         <v>345.8827387645665</v>
@@ -6858,22 +6858,22 @@
         <v>1324.818077814764</v>
       </c>
       <c r="M34" t="n">
-        <v>1120.139682458653</v>
+        <v>1324.818077814764</v>
       </c>
       <c r="N34" t="n">
-        <v>864.3971821842238</v>
+        <v>1069.075577540335</v>
       </c>
       <c r="O34" t="n">
-        <v>864.3971821842238</v>
+        <v>743.3729875615318</v>
       </c>
       <c r="P34" t="n">
-        <v>510.5405516449025</v>
+        <v>370.1932932905444</v>
       </c>
       <c r="Q34" t="n">
-        <v>98.58169666955095</v>
+        <v>53.76</v>
       </c>
       <c r="R34" t="n">
-        <v>98.58169666955095</v>
+        <v>53.76</v>
       </c>
       <c r="S34" t="n">
         <v>53.76</v>
@@ -6904,37 +6904,37 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L35" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M35" t="n">
         <v>690.5809049473327</v>
@@ -6943,7 +6943,7 @@
         <v>1243.990904947333</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P35" t="n">
         <v>1797.400904947332</v>
@@ -6952,28 +6952,28 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>391.4553531635761</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C36" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U36" t="n">
-        <v>695.1871702940784</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V36" t="n">
-        <v>630.0248802016338</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W36" t="n">
-        <v>546.8196853432211</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X36" t="n">
-        <v>476.2512616610114</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y36" t="n">
-        <v>426.3609659376434</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
         <v>103.3156148520479</v>
@@ -7165,19 +7165,19 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L38" t="n">
-        <v>598.13</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M38" t="n">
-        <v>1108.978828728935</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N38" t="n">
-        <v>1662.388828728935</v>
+        <v>1682.59</v>
       </c>
       <c r="O38" t="n">
         <v>1682.59</v>
@@ -7201,16 +7201,16 @@
         <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>391.4553531635761</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
         <v>44.72</v>
@@ -7271,25 +7271,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>801.8216399685234</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T39" t="n">
-        <v>745.9047054053782</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U39" t="n">
-        <v>695.1871702940784</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V39" t="n">
-        <v>630.0248802016338</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W39" t="n">
-        <v>546.8196853432211</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X39" t="n">
-        <v>476.2512616610114</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>426.3609659376434</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7402,25 +7402,25 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>179.7320762183974</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>733.1420762183974</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>1286.552076218397</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M41" t="n">
-        <v>1797.400904947332</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N41" t="n">
-        <v>1797.400904947332</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>402.0654643105373</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E42" t="n">
         <v>44.72</v>
@@ -7520,13 +7520,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>444.3729990826727</v>
+        <v>436.9710770846045</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D43" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H43" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J43" t="n">
         <v>1860.696627021627</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
         <v>44.72</v>
@@ -7639,19 +7639,19 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="K44" t="n">
-        <v>44.72</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L44" t="n">
-        <v>598.13</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M44" t="n">
-        <v>1108.978828728935</v>
+        <v>1129.18</v>
       </c>
       <c r="N44" t="n">
-        <v>1662.388828728935</v>
+        <v>1129.18</v>
       </c>
       <c r="O44" t="n">
         <v>1682.59</v>
@@ -7663,28 +7663,28 @@
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>119.2429040110725</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C45" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D45" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E45" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F45" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7748,22 +7748,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>753.4482964674547</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>702.730761356155</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>637.5684712637103</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>554.3632764052976</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.1485167851398</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="46">
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,16 +7973,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>929.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>439.6923140185369</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>369.7315044851258</v>
       </c>
       <c r="Q2" t="n">
         <v>557.8226843274854</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>404.4874506895348</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
         <v>929.2621276423173</v>
@@ -8681,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>184.1434931650601</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,13 +8690,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8927,10 +8927,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>606.6620109882336</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>536.7012014548227</v>
       </c>
       <c r="Q14" t="n">
         <v>172.8226843274854</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>193.2279078336117</v>
+        <v>313.9750954005603</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,25 +9389,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
+        <v>93.38475247205329</v>
+      </c>
+      <c r="L20" t="n">
         <v>559</v>
       </c>
-      <c r="L20" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.24895806984</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>90.65309308021371</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>637.6468801143475</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>1036.248958069844</v>
+        <v>777.3630622928066</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740999</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406882</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9863,25 +9863,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>672</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>704.7963172314074</v>
+        <v>742.2478695741012</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>672.2870600406914</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>422.4094388348857</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
         <v>672</v>
@@ -10106,16 +10106,16 @@
         <v>672</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>726.8357125772527</v>
+        <v>606.0885250103026</v>
       </c>
       <c r="O29" t="n">
-        <v>742.2478695740936</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>672.2870600406839</v>
       </c>
       <c r="Q29" t="n">
         <v>172.8226843274854</v>
@@ -10334,25 +10334,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1022.819493207646</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>835.059136068212</v>
       </c>
       <c r="O32" t="n">
         <v>742.247869574094</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>672.2870600406843</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,25 +10571,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>801.385149773304</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,22 +10808,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>618.4013691429103</v>
       </c>
       <c r="O38" t="n">
-        <v>90.65309308021877</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
         <v>559.2870600406815</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>171.4188408091281</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>211.4002806471676</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>55.44822975121687</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11294,10 +11294,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
-        <v>90.65309308021877</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
         <v>559.2870600406815</v>
@@ -22715,10 +22715,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.59117064605573</v>
       </c>
       <c r="R4" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22952,10 +22952,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59117064605573</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.59117064605033</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -24596,25 +24596,25 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>105.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>253.1850752716849</v>
+        <v>178.0980164236883</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>369.4478973282775</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>391.4448217250514</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24705,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.504208614527499</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.504208614585508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24833,28 +24833,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>105.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>253.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>322.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>180.7268699700952</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>68.99925764603648</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>44.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24894,7 +24894,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>5.504208614585579</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>5.504208614524913</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25073,25 +25073,25 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>322.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>19.12983309434941</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>94.570306067959</v>
       </c>
       <c r="R34" t="n">
         <v>408.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>44.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9486324.848666824</v>
+        <v>9486324.84866683</v>
       </c>
     </row>
     <row r="12">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13245281.80689695</v>
+        <v>13245281.80689696</v>
       </c>
     </row>
     <row r="16">
@@ -26275,7 +26275,7 @@
         <v>1259338.852237089</v>
       </c>
       <c r="D2" t="n">
-        <v>1259338.85223709</v>
+        <v>1259338.852237089</v>
       </c>
       <c r="E2" t="n">
         <v>1259377.040332595</v>
@@ -26293,13 +26293,13 @@
         <v>1259377.040332595</v>
       </c>
       <c r="J2" t="n">
+        <v>1240934.644723165</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1240934.64472317</v>
+      </c>
+      <c r="L2" t="n">
         <v>1240934.644723166</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1240934.644723166</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1240934.64472317</v>
       </c>
       <c r="M2" t="n">
         <v>1259377.040332595</v>
@@ -26311,7 +26311,7 @@
         <v>1259377.040332595</v>
       </c>
       <c r="P2" t="n">
-        <v>1259377.040332596</v>
+        <v>1259377.040332595</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540106</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.3079521839</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>509242.089049618</v>
+        <v>511130.7051621593</v>
       </c>
       <c r="K4" t="n">
-        <v>507410.0945171365</v>
+        <v>509298.7106296805</v>
       </c>
       <c r="L4" t="n">
-        <v>505575.4970691516</v>
+        <v>507464.1131816903</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495869.1273375804</v>
+        <v>494353.2716492646</v>
       </c>
       <c r="C6" t="n">
-        <v>633447.1074713945</v>
+        <v>631931.2517830788</v>
       </c>
       <c r="D6" t="n">
-        <v>635507.8793837108</v>
+        <v>633992.0236953943</v>
       </c>
       <c r="E6" t="n">
-        <v>311623.6371060599</v>
+        <v>309881.7872929523</v>
       </c>
       <c r="F6" t="n">
-        <v>654814.5324515639</v>
+        <v>653072.682638456</v>
       </c>
       <c r="G6" t="n">
-        <v>656760.10891975</v>
+        <v>655018.2591066415</v>
       </c>
       <c r="H6" t="n">
-        <v>658708.3857370507</v>
+        <v>656966.5359239435</v>
       </c>
       <c r="I6" t="n">
-        <v>660659.3823804115</v>
+        <v>658917.5325673035</v>
       </c>
       <c r="J6" t="n">
-        <v>234405.013673548</v>
+        <v>232516.3975610057</v>
       </c>
       <c r="K6" t="n">
-        <v>665933.0082060291</v>
+        <v>664044.39209349</v>
       </c>
       <c r="L6" t="n">
-        <v>667767.6056540186</v>
+        <v>665878.9895414754</v>
       </c>
       <c r="M6" t="n">
-        <v>621418.9657904943</v>
+        <v>619677.1159773867</v>
       </c>
       <c r="N6" t="n">
-        <v>670455.8628253482</v>
+        <v>668714.0130122402</v>
       </c>
       <c r="O6" t="n">
-        <v>418023.6020830858</v>
+        <v>416281.7522699781</v>
       </c>
       <c r="P6" t="n">
-        <v>674394.2049340967</v>
+        <v>672652.3551209887</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -27036,16 +27036,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>61</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27481,13 +27481,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27572,16 +27572,16 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>29.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>41.09317658208397</v>
       </c>
       <c r="Y3" t="n">
-        <v>302.3607521730194</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,31 +27594,31 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>377.6794899898316</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>177.7033820564725</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,13 +27645,13 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27727,10 +27727,10 @@
         <v>400</v>
       </c>
       <c r="U5" t="n">
+        <v>400</v>
+      </c>
+      <c r="V5" t="n">
         <v>371.2938086145854</v>
-      </c>
-      <c r="V5" t="n">
-        <v>400</v>
       </c>
       <c r="W5" t="n">
         <v>400</v>
@@ -27758,16 +27758,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>10.65259501914073</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>139.8182410159025</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>47.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,25 +27828,25 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>385.6192724710594</v>
+      </c>
+      <c r="C7" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D7" t="n">
         <v>400</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>400</v>
       </c>
-      <c r="D7" t="n">
-        <v>285.5362180555555</v>
-      </c>
-      <c r="E7" t="n">
-        <v>280.9809048369565</v>
-      </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>290.9590160494047</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X7" t="n">
         <v>400</v>
-      </c>
-      <c r="X7" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -27998,13 +27998,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>168.7500662750006</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>179.8242334605118</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>20.35776521751382</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28071,13 +28071,13 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>245.04387284153</v>
@@ -28086,13 +28086,13 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>231.3704704183498</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>290.3572801238425</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28147,13 +28147,13 @@
         <v>350</v>
       </c>
       <c r="C11" t="n">
+        <v>350</v>
+      </c>
+      <c r="D11" t="n">
+        <v>350</v>
+      </c>
+      <c r="E11" t="n">
         <v>346.0346086145855</v>
-      </c>
-      <c r="D11" t="n">
-        <v>350</v>
-      </c>
-      <c r="E11" t="n">
-        <v>350</v>
       </c>
       <c r="F11" t="n">
         <v>350</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>350</v>
@@ -28232,13 +28232,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964701</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>263.0617733495849</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
         <v>332.1680871864211</v>
@@ -28277,7 +28277,7 @@
         <v>350</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U12" t="n">
         <v>350</v>
@@ -28429,10 +28429,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28481,7 +28481,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
-        <v>154.4486233659061</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28514,7 +28514,7 @@
         <v>350</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="U15" t="n">
         <v>350</v>
@@ -28529,7 +28529,7 @@
         <v>350</v>
       </c>
       <c r="Y15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28621,7 +28621,7 @@
         <v>350</v>
       </c>
       <c r="C17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="D17" t="n">
         <v>350</v>
@@ -28636,7 +28636,7 @@
         <v>350</v>
       </c>
       <c r="H17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I17" t="n">
         <v>150.0811596826846</v>
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964701</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28718,7 +28718,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28864,13 +28864,13 @@
         <v>350</v>
       </c>
       <c r="E20" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="F20" t="n">
         <v>350</v>
       </c>
       <c r="G20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H20" t="n">
         <v>350</v>
@@ -28940,22 +28940,22 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>260.9994602472874</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>144.0848657037828</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29177,10 +29177,10 @@
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29192,7 +29192,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29222,7 +29222,7 @@
         <v>350</v>
       </c>
       <c r="S24" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="T24" t="n">
         <v>350</v>
@@ -29429,13 +29429,13 @@
         <v>318</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>222.713455571481</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>5.587069680132458</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283537</v>
       </c>
       <c r="S29" t="n">
         <v>318</v>
@@ -29654,7 +29654,7 @@
         <v>318</v>
       </c>
       <c r="E30" t="n">
-        <v>318</v>
+        <v>318.000000000033</v>
       </c>
       <c r="F30" t="n">
         <v>318</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>178.6663347706119</v>
+        <v>178.6663347705784</v>
       </c>
       <c r="R30" t="n">
         <v>318</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>250.8785988283564</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>318</v>
@@ -29903,7 +29903,7 @@
         <v>318</v>
       </c>
       <c r="I33" t="n">
-        <v>222.7134555714511</v>
+        <v>222.7134555714475</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29942,13 +29942,13 @@
         <v>318</v>
       </c>
       <c r="V33" t="n">
-        <v>318</v>
+        <v>318.0000000000329</v>
       </c>
       <c r="W33" t="n">
         <v>318</v>
       </c>
       <c r="X33" t="n">
-        <v>318.0000000000293</v>
+        <v>318</v>
       </c>
       <c r="Y33" t="n">
         <v>318</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30137,7 +30137,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
         <v>217.1263858913485</v>
@@ -30167,7 +30167,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30176,7 +30176,7 @@
         <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>269.4903246609787</v>
+        <v>350</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -30188,7 +30188,7 @@
         <v>350</v>
       </c>
       <c r="Y36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30292,7 +30292,7 @@
         <v>350</v>
       </c>
       <c r="G38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H38" t="n">
         <v>350</v>
@@ -30337,7 +30337,7 @@
         <v>350</v>
       </c>
       <c r="V38" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="W38" t="n">
         <v>350</v>
@@ -30374,7 +30374,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30407,7 +30407,7 @@
         <v>350</v>
       </c>
       <c r="S39" t="n">
-        <v>269.4903246609786</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>350</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
     </row>
     <row r="40">
@@ -30435,61 +30435,61 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>350</v>
+      </c>
+      <c r="C40" t="n">
+        <v>350</v>
+      </c>
+      <c r="D40" t="n">
+        <v>350</v>
+      </c>
+      <c r="E40" t="n">
+        <v>350</v>
+      </c>
+      <c r="F40" t="n">
+        <v>350</v>
+      </c>
+      <c r="G40" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
+        <v>350</v>
+      </c>
+      <c r="L40" t="n">
+        <v>350</v>
+      </c>
+      <c r="M40" t="n">
+        <v>350</v>
+      </c>
+      <c r="N40" t="n">
+        <v>350</v>
+      </c>
+      <c r="O40" t="n">
+        <v>350</v>
+      </c>
+      <c r="P40" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>350</v>
+      </c>
+      <c r="R40" t="n">
+        <v>350</v>
+      </c>
+      <c r="S40" t="n">
+        <v>350</v>
+      </c>
+      <c r="T40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="C40" t="n">
-        <v>350</v>
-      </c>
-      <c r="D40" t="n">
-        <v>350</v>
-      </c>
-      <c r="E40" t="n">
-        <v>350</v>
-      </c>
-      <c r="F40" t="n">
-        <v>350</v>
-      </c>
-      <c r="G40" t="n">
-        <v>350</v>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="n">
-        <v>350</v>
-      </c>
-      <c r="J40" t="n">
-        <v>350</v>
-      </c>
-      <c r="K40" t="n">
-        <v>350</v>
-      </c>
-      <c r="L40" t="n">
-        <v>350</v>
-      </c>
-      <c r="M40" t="n">
-        <v>350</v>
-      </c>
-      <c r="N40" t="n">
-        <v>350</v>
-      </c>
-      <c r="O40" t="n">
-        <v>350</v>
-      </c>
-      <c r="P40" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>350</v>
-      </c>
-      <c r="R40" t="n">
-        <v>350</v>
-      </c>
-      <c r="S40" t="n">
-        <v>350</v>
-      </c>
-      <c r="T40" t="n">
-        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
@@ -30602,7 +30602,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
@@ -30656,13 +30656,13 @@
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X42" t="n">
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>350</v>
+        <v>279.99433469647</v>
       </c>
     </row>
     <row r="43">
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30769,7 +30769,7 @@
         <v>350</v>
       </c>
       <c r="H44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I44" t="n">
         <v>150.0811596826846</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30842,13 +30842,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>269.4903246609787</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30884,7 +30884,7 @@
         <v>350</v>
       </c>
       <c r="T45" t="n">
-        <v>350</v>
+        <v>276.9584798124345</v>
       </c>
       <c r="U45" t="n">
         <v>350</v>
@@ -30899,7 +30899,7 @@
         <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46">
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34752,16 +34752,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>385</v>
       </c>
-      <c r="N2" t="n">
-        <v>385</v>
-      </c>
-      <c r="O2" t="n">
-        <v>369.4444444444445</v>
-      </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="Q2" t="n">
         <v>385</v>
@@ -34880,31 +34880,31 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>96.698585152875</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.069926436354184</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34931,13 +34931,13 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -35114,25 +35114,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>98.50547213398072</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>80.93444954314704</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>385</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>385</v>
@@ -35357,13 +35357,13 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35372,13 +35372,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>4.997660579640111</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.891927274380132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35460,7 +35460,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>184.1434931650601</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,13 +35469,13 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35706,10 +35706,10 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>536.4141414141411</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.40522350612631</v>
+        <v>141.1524110730749</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,25 +36168,25 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>93.38475247205329</v>
+      </c>
+      <c r="L20" t="n">
         <v>559</v>
       </c>
-      <c r="L20" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>559.000000000005</v>
+        <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>20.40522350612126</v>
+        <v>559</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>93.38475247203016</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>559.0000000000086</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="O23" t="n">
-        <v>559.0000000000075</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>559.0000000000067</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36642,25 +36642,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>672</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>634.5484476573149</v>
+        <v>672.0000000000088</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>672.0000000000099</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>249.5867545074003</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,13 +36715,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5.587069680132455</v>
       </c>
       <c r="J27" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>196.6909243209238</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>274.091375348687</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>672</v>
@@ -36885,22 +36885,22 @@
         <v>672</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>249.5867545074175</v>
+        <v>128.8395669404674</v>
       </c>
       <c r="O29" t="n">
-        <v>672.0000000000011</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>672.0000000000024</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5.925495784278169e-11</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -36976,7 +36976,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.587069680132347</v>
+        <v>5.587069680098815</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,31 +37113,31 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>478.5573655653287</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>357.8101779983768</v>
       </c>
       <c r="O32" t="n">
         <v>672.0000000000016</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>672.0000000000028</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
-        <v>6.201100239360875e-11</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>5.587069680102598</v>
+        <v>5.587069680098923</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37350,25 +37350,25 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>257.1230221309867</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
       </c>
       <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>559</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>443.0293889420883</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,22 +37587,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>559</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="O38" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>559</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C40" t="n">
         <v>77.27475335195533</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>136.3758345640378</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>559</v>
       </c>
-      <c r="M41" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>20.40522350612654</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -38073,10 +38073,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>559</v>
-      </c>
-      <c r="O44" t="n">
-        <v>20.40522350612631</v>
       </c>
       <c r="P44" t="n">
         <v>559</v>
